--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104612_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104612_W18.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.4713</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4471</v>
+        <v>0.9151</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3317</v>
+        <v>-0.4437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3809</v>
+        <v>-2.2195</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6768</v>
+        <v>-0.7673</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2958</v>
+        <v>-1.4522</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4227</v>
+        <v>-0.0974</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3853</v>
+        <v>0.655</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0373</v>
+        <v>-0.7524</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0417</v>
+        <v>-2.1221</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7086</v>
+        <v>-1.4223</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3331</v>
+        <v>-0.6998</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1859</v>
+        <v>1.1461</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1735</v>
+        <v>1.0611</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0124</v>
+        <v>0.0849</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5436</v>
+        <v>0.3816</v>
       </c>
       <c r="E3" t="n">
-        <v>1.041</v>
+        <v>-1.7381</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4974</v>
+        <v>2.1197</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.2303</v>
+        <v>-3.8633</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.775</v>
+        <v>-0.8973</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4554</v>
+        <v>-2.966</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.091</v>
+        <v>-2.6612</v>
       </c>
       <c r="K3" t="n">
-        <v>0.658</v>
+        <v>-0.1356</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.749</v>
+        <v>-2.5255</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1393</v>
+        <v>-1.2022</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.433</v>
+        <v>-0.7617</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7063</v>
+        <v>-0.4405</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>2.9592</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2276</v>
+        <v>1.0173</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1735</v>
+        <v>0.6546</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0541</v>
+        <v>0.3627</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1434</v>
+        <v>-0.0161</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.3578</v>
+        <v>-0.3309</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2144</v>
+        <v>0.3148</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.8282</v>
+        <v>0.3848</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8667</v>
+        <v>0.675</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.9614</v>
+        <v>-0.2902</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.6056</v>
+        <v>1.4162</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0946</v>
+        <v>1.3789</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.511</v>
+        <v>0.0372</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2225</v>
+        <v>-1.0314</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7721</v>
+        <v>-0.7039</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4504</v>
+        <v>-0.3275</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-3.4145</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9488</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4579</v>
+        <v>0.4005</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0302</v>
+        <v>0.4202</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4881</v>
+        <v>-0.0196</v>
       </c>
       <c r="V4" t="n">
-        <v>1.639</v>
+        <v>1.2472</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639</v>
+        <v>1.2472</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0681</v>
+        <v>-0.632</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3928</v>
+        <v>-1.0705</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3247</v>
+        <v>0.4385</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9321</v>
+        <v>-1.9217</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2396</v>
+        <v>-0.2357</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6926</v>
+        <v>-1.686</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5732</v>
+        <v>-0.5773</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.359</v>
+        <v>-1.3444</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5012</v>
+        <v>0.9255</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4053</v>
+        <v>0.736</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0959</v>
+        <v>0.1895</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0961</v>
+        <v>-1.0699</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1123</v>
+        <v>-1.1233</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0163</v>
+        <v>0.0534</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0097</v>
+        <v>0.0083</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6754</v>
+        <v>-0.6722</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6806</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3878</v>
+        <v>0.3819</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2755</v>
+        <v>-0.2451</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1681</v>
+        <v>-1.8426</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5803</v>
+        <v>-1.147</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5878</v>
+        <v>-0.6956</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7806</v>
+        <v>-2.7959</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4558</v>
+        <v>-1.467</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3248</v>
+        <v>-1.3289</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0959</v>
+        <v>1.0442</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7335</v>
+        <v>0.7025</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3623</v>
+        <v>0.3417</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.8764</v>
+        <v>-3.8401</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1893</v>
+        <v>-2.1695</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6871</v>
+        <v>-1.6706</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.083</v>
+        <v>-4.0974</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7466</v>
+        <v>2.0915</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2461</v>
+        <v>1.7484</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.343</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. BURJANADZE</t>
+          <t>A. ALIBEGOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4311</v>
+        <v>-2.6187</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.9356</v>
+        <v>-1.7642</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5045</v>
+        <v>-0.8546</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.3063</v>
+        <v>-4.0379</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0618</v>
+        <v>-1.787</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2444</v>
+        <v>-2.2509</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.4487</v>
+        <v>-1.7174</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1642</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.2844</v>
+        <v>-1.0656</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8576</v>
+        <v>-2.3205</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8976</v>
+        <v>-1.1353</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04</v>
+        <v>-1.1852</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8147</v>
+        <v>-0.4553</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4952</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8888</v>
+        <v>0.281</v>
       </c>
       <c r="T8" t="n">
-        <v>2.099</v>
+        <v>0.4085</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2102</v>
+        <v>-0.1275</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6941000000000001</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>B. BURJANADZE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3246</v>
+        <v>-3.0875</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4872</v>
+        <v>-4.7686</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8374</v>
+        <v>1.6811</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8586</v>
+        <v>-4.3199</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7951</v>
+        <v>-2.0703</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0635</v>
+        <v>-2.2495</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4139</v>
+        <v>-3.474</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3392</v>
+        <v>-1.1796</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>-2.2945</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2725</v>
+        <v>-0.8458</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1344</v>
+        <v>-0.8907</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1381</v>
+        <v>0.0449</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.1757</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.8562</v>
+        <v>-1.8211</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>2.5039</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9255</v>
+        <v>1.246</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7017</v>
+        <v>1.3005</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2238</v>
+        <v>-0.0545</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7842</v>
+        <v>-0.6966</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2534</v>
+        <v>-0.7739</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4692</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ALIBEGOVIC</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5022</v>
+        <v>-3.3222</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4297</v>
+        <v>-1.5115</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0725</v>
+        <v>-1.8108</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.0478</v>
+        <v>-1.8443</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7981</v>
+        <v>-0.7901</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2497</v>
+        <v>-1.0542</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7008</v>
+        <v>0.4052</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6478</v>
+        <v>0.3308</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.053</v>
+        <v>0.0745</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.347</v>
+        <v>-2.2496</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1503</v>
+        <v>-1.1209</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1967</v>
+        <v>-1.1287</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.4537</v>
+        <v>-3.8697</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5886</v>
+        <v>0.929</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2752</v>
+        <v>0.7058</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3133</v>
+        <v>0.2232</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.7799</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.4673</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7806</v>
+        <v>-3.3835</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6602</v>
+        <v>-2.2665</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1204</v>
+        <v>-1.117</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5768</v>
+        <v>-3.5734</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1081</v>
+        <v>-2.1108</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4687</v>
+        <v>-1.4625</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2226</v>
+        <v>-0.2475</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1079</v>
+        <v>-0.1281</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3542</v>
+        <v>-3.3258</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.0002</v>
+        <v>-1.9827</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3995</v>
+        <v>0.7954</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5111</v>
+        <v>0.9403</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1116</v>
+        <v>-0.1449</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9233</v>
+        <v>-5.9605</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8514</v>
+        <v>-5.7684</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.1921</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.8017</v>
+        <v>-4.7936</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.3188</v>
+        <v>-5.3136</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5171</v>
+        <v>0.52</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0047</v>
+        <v>-2.0257</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.9723</v>
+        <v>-2.9862</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.7969</v>
+        <v>-2.7679</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.3466</v>
+        <v>-2.3274</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.2172</v>
+        <v>-5.2355</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3625</v>
+        <v>1.3296</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2098</v>
+        <v>1.3351</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1527</v>
+        <v>-0.0055</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2378</v>
+        <v>0.2352</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.1152</v>
+        <v>-21.0801</v>
       </c>
       <c r="E13" t="n">
-        <v>-21.3192</v>
+        <v>-20.5739</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7958000000000002</v>
+        <v>-0.5063</v>
       </c>
       <c r="G13" t="n">
-        <v>-28.9718</v>
+        <v>-28.9764</v>
       </c>
       <c r="H13" t="n">
-        <v>-15.4176</v>
+        <v>-15.4363</v>
       </c>
       <c r="I13" t="n">
-        <v>-13.5542</v>
+        <v>-13.5398</v>
       </c>
       <c r="J13" t="n">
-        <v>-7.3263</v>
+        <v>-7.553000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.715</v>
+        <v>-1.8589</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.6116</v>
+        <v>-5.694000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-21.6452</v>
+        <v>-21.4234</v>
       </c>
       <c r="N13" t="n">
-        <v>-13.7029</v>
+        <v>-13.5775</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.9424</v>
+        <v>-7.846</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.670799999999999</v>
+        <v>-5.6907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-26.086</v>
+        <v>-26.1778</v>
       </c>
       <c r="R13" t="n">
-        <v>20.4149</v>
+        <v>20.4867</v>
       </c>
       <c r="S13" t="n">
-        <v>8.8314</v>
+        <v>9.9168</v>
       </c>
       <c r="T13" t="n">
-        <v>8.0755</v>
+        <v>9.171099999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.756</v>
+        <v>0.7455999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>3.696</v>
+        <v>3.6703</v>
       </c>
       <c r="W13" t="n">
-        <v>4.0175</v>
+        <v>3.9859</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3215</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0926</v>
+        <v>5.324</v>
       </c>
       <c r="E14" t="n">
-        <v>1.511</v>
+        <v>4.3442</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5816</v>
+        <v>0.9798</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4316</v>
+        <v>6.6013</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0317</v>
+        <v>3.6044</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3999</v>
+        <v>2.9969</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3192</v>
+        <v>4.5046</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8443</v>
+        <v>2.2408</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5251</v>
+        <v>2.2638</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1124</v>
+        <v>2.0967</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1874</v>
+        <v>1.3636</v>
       </c>
       <c r="O14" t="n">
-        <v>0.925</v>
+        <v>0.7331</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9488</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0051</v>
+        <v>-0.534</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6079</v>
+        <v>0.0673</v>
       </c>
       <c r="U14" t="n">
-        <v>0.613</v>
+        <v>-0.6012</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-2.3367</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9455</v>
+        <v>5.1179</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2465</v>
+        <v>1.7177</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6989</v>
+        <v>3.4002</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6044</v>
+        <v>4.4339</v>
       </c>
       <c r="H15" t="n">
-        <v>3.603</v>
+        <v>4.0269</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0013</v>
+        <v>0.407</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5248</v>
+        <v>3.2976</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2512</v>
+        <v>3.8266</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2736</v>
+        <v>-0.529</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0796</v>
+        <v>1.1363</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3519</v>
+        <v>0.2003</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7277</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>2.9592</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9006999999999999</v>
+        <v>0.0223</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0514</v>
+        <v>-0.3719</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8493000000000001</v>
+        <v>0.3942</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.3461</v>
+        <v>-0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3461</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9568</v>
+        <v>3.993</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8224</v>
+        <v>1.5419</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1345</v>
+        <v>2.4511</v>
       </c>
       <c r="G16" t="n">
-        <v>5.9747</v>
+        <v>5.9632</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8023</v>
+        <v>3.7944</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1724</v>
+        <v>2.1687</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9023</v>
+        <v>4.8718</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3004</v>
+        <v>3.2783</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0724</v>
+        <v>1.0914</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1747</v>
+        <v>-1.1311</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2299</v>
+        <v>-0.0049</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4046</v>
+        <v>-1.1262</v>
       </c>
       <c r="V16" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3297</v>
+        <v>3.5757</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6641</v>
+        <v>0.2759</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6656</v>
+        <v>3.2998</v>
       </c>
       <c r="G17" t="n">
-        <v>4.5623</v>
+        <v>4.5673</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8381</v>
+        <v>1.849</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7241</v>
+        <v>2.7183</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2257</v>
+        <v>3.2005</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5817</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6441</v>
+        <v>2.6285</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3365</v>
+        <v>1.3668</v>
       </c>
       <c r="N17" t="n">
-        <v>1.2565</v>
+        <v>1.277</v>
       </c>
       <c r="O17" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="R17" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3668</v>
+        <v>-1.1297</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3871</v>
+        <v>0.0346</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.7539</v>
+        <v>-1.1644</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3695</v>
+        <v>3.2729</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0603</v>
+        <v>-0.6032</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4298</v>
+        <v>3.8761</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7548</v>
+        <v>3.55</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0982</v>
+        <v>-0.451</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.853</v>
+        <v>4.001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1423</v>
+        <v>2.7874</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2326</v>
+        <v>0.1961</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.0903</v>
+        <v>2.5912</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8971</v>
+        <v>0.7627</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1344</v>
+        <v>-0.6471</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2373</v>
+        <v>1.4097</v>
       </c>
       <c r="P18" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5878</v>
+        <v>-2.7316</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9488</v>
+        <v>3.1868</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7632</v>
+        <v>-1.1194</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3852</v>
+        <v>-0.272</v>
       </c>
       <c r="U18" t="n">
-        <v>0.378</v>
+        <v>-0.8474</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2397</v>
+        <v>3.0714</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0086</v>
+        <v>0.344</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2311</v>
+        <v>2.7274</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7876</v>
+        <v>1.7903</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8756</v>
+        <v>1.8891</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0881</v>
+        <v>-0.0988</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7738</v>
+        <v>0.7554</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7446</v>
+        <v>0.7412</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0138</v>
+        <v>1.0349</v>
       </c>
       <c r="N19" t="n">
-        <v>1.131</v>
+        <v>1.1479</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8162</v>
+        <v>-0.9952</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5383</v>
+        <v>-0.1838</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2778</v>
+        <v>-0.8115</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.138</v>
+        <v>2.3138</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.916</v>
+        <v>-0.6923</v>
       </c>
       <c r="F20" t="n">
-        <v>3.054</v>
+        <v>3.006</v>
       </c>
       <c r="G20" t="n">
-        <v>3.5519</v>
+        <v>3.7817</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4517</v>
+        <v>1.5308</v>
       </c>
       <c r="I20" t="n">
-        <v>4.0036</v>
+        <v>2.2509</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8177</v>
+        <v>3.1336</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2109</v>
+        <v>1.5029</v>
       </c>
       <c r="L20" t="n">
-        <v>2.6068</v>
+        <v>1.6308</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7343</v>
+        <v>0.6481</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6626</v>
+        <v>0.028</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3968</v>
+        <v>0.6201</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.722</v>
+        <v>-3.6421</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1757</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2532</v>
+        <v>-0.1021</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6261</v>
+        <v>-0.1838</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.6272</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.369</v>
+        <v>1.3484</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0117</v>
+        <v>-1.2746</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3807</v>
+        <v>2.623</v>
       </c>
       <c r="G21" t="n">
-        <v>3.7807</v>
+        <v>-0.7629</v>
       </c>
       <c r="H21" t="n">
-        <v>1.531</v>
+        <v>0.0922</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2497</v>
+        <v>-0.8551</v>
       </c>
       <c r="J21" t="n">
-        <v>3.156</v>
+        <v>0.1102</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5168</v>
+        <v>1.2131</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6392</v>
+        <v>-1.1029</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6247</v>
+        <v>-0.8731</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0142</v>
+        <v>-1.1209</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6105</v>
+        <v>0.2477</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6293</v>
+        <v>-1.5934</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2683</v>
+        <v>2.9592</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0507</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5383</v>
+        <v>0.2086</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5123</v>
+        <v>0.5369</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0501</v>
+        <v>-0.015</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1247</v>
+        <v>-0.0895</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1572</v>
+        <v>-0.1544</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="I22" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2318</v>
+        <v>-0.2289</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1071</v>
+        <v>0.1394</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1071</v>
+        <v>0.1394</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8534</v>
+        <v>-0.0248</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8438</v>
+        <v>-1.6186</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9903</v>
+        <v>1.5938</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2989</v>
+        <v>-1.2515</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1096</v>
+        <v>-0.833</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1893</v>
+        <v>-0.4186</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0556</v>
+        <v>-1.3954</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.09370000000000001</v>
+        <v>0.0722</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1493</v>
+        <v>-1.4676</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2433</v>
+        <v>0.1438</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2033</v>
+        <v>-0.9052</v>
       </c>
       <c r="O23" t="n">
-        <v>0.04</v>
+        <v>1.049</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4718</v>
+        <v>-0.0512</v>
       </c>
       <c r="T23" t="n">
-        <v>0.369</v>
+        <v>-0.2232</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8408</v>
+        <v>0.1721</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9812</v>
+        <v>-0.4929</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0769</v>
+        <v>-1.9746</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0957</v>
+        <v>1.4817</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2525</v>
+        <v>0.3085</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.834</v>
+        <v>0.1146</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4185</v>
+        <v>0.1939</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3813</v>
+        <v>0.0488</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0795</v>
+        <v>-0.1002</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4608</v>
+        <v>0.1489</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1288</v>
+        <v>0.2597</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9135</v>
+        <v>0.2148</v>
       </c>
       <c r="O24" t="n">
-        <v>1.0423</v>
+        <v>0.0449</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5878</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.995</v>
+        <v>-0.1184</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6956</v>
+        <v>0.253</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2994</v>
+        <v>-0.3714</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.4409</v>
+        <v>-1.4106</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6228</v>
+        <v>-1.6286</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1819</v>
+        <v>0.2181</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1442</v>
+        <v>0.1491</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0131</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6778</v>
+        <v>-0.6491</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6082</v>
+        <v>-0.5794</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>22.1152</v>
+        <v>26.0738</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7956999999999999</v>
+        <v>0.5063</v>
       </c>
       <c r="F26" t="n">
-        <v>21.3194</v>
+        <v>25.5675</v>
       </c>
       <c r="G26" t="n">
-        <v>28.9718</v>
+        <v>28.9765</v>
       </c>
       <c r="H26" t="n">
-        <v>15.4175</v>
+        <v>15.4362</v>
       </c>
       <c r="I26" t="n">
-        <v>13.554</v>
+        <v>13.5401</v>
       </c>
       <c r="J26" t="n">
-        <v>21.6453</v>
+        <v>21.4235</v>
       </c>
       <c r="K26" t="n">
-        <v>13.7029</v>
+        <v>13.5776</v>
       </c>
       <c r="L26" t="n">
-        <v>7.9425</v>
+        <v>7.8459</v>
       </c>
       <c r="M26" t="n">
-        <v>7.3265</v>
+        <v>7.552999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7148</v>
+        <v>1.8589</v>
       </c>
       <c r="O26" t="n">
-        <v>5.6116</v>
+        <v>5.693899999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>5.670799999999999</v>
+        <v>5.690799999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-20.4148</v>
+        <v>-20.4867</v>
       </c>
       <c r="R26" t="n">
-        <v>26.0857</v>
+        <v>26.1775</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.8315</v>
+        <v>-4.922999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7560000000000001</v>
+        <v>-0.7458</v>
       </c>
       <c r="U26" t="n">
-        <v>-8.0754</v>
+        <v>-4.1773</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.696</v>
+        <v>-3.6702</v>
       </c>
       <c r="W26" t="n">
-        <v>0.3214000000000001</v>
+        <v>0.3154999999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.0175</v>
+        <v>-3.985799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104612_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104612_W18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.4673</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104612_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-3.985799999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
